--- a/ProyectoAsistencia/ReporteClasesDeLaboratorio.xlsx
+++ b/ProyectoAsistencia/ReporteClasesDeLaboratorio.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="169">
   <si>
     <t>Nro Laboratorio</t>
   </si>
@@ -29,10 +29,13 @@
     <t>Hora Inicio</t>
   </si>
   <si>
-    <t>HoraFin</t>
-  </si>
-  <si>
-    <t>Codgio de Horario</t>
+    <t>Hora Fin</t>
+  </si>
+  <si>
+    <t>Fecha Inicio</t>
+  </si>
+  <si>
+    <t>Codigo de Horario</t>
   </si>
   <si>
     <t>LAB-101</t>
@@ -53,6 +56,9 @@
     <t>10:00:00</t>
   </si>
   <si>
+    <t>02-12-2024</t>
+  </si>
+  <si>
     <t>HS01</t>
   </si>
   <si>
@@ -65,6 +71,9 @@
     <t>MARTES</t>
   </si>
   <si>
+    <t>fechaaCom</t>
+  </si>
+  <si>
     <t>HS07</t>
   </si>
   <si>
@@ -134,6 +143,9 @@
     <t>12:00:00</t>
   </si>
   <si>
+    <t>03-12-2024</t>
+  </si>
+  <si>
     <t>HS02</t>
   </si>
   <si>
@@ -185,15 +197,45 @@
     <t>HS38</t>
   </si>
   <si>
+    <t>luismartinez</t>
+  </si>
+  <si>
+    <t>Martes</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>24-12-2024</t>
+  </si>
+  <si>
+    <t>lab102_martes_luismartinez_matematicas_ii_12y00_15y00</t>
+  </si>
+  <si>
+    <t>Miercoles</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>25-12-2024</t>
+  </si>
+  <si>
+    <t>lab102_miercoles_luismartinez_matematicas_ii_14y00_16y00</t>
+  </si>
+  <si>
     <t>LAB-103</t>
   </si>
   <si>
     <t>Física I</t>
   </si>
   <si>
-    <t>luismartinez</t>
-  </si>
-  <si>
     <t>14:00:00</t>
   </si>
   <si>
@@ -248,6 +290,48 @@
     <t>HS39</t>
   </si>
   <si>
+    <t>elenamolina</t>
+  </si>
+  <si>
+    <t>Lunes</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>16-12-2024</t>
+  </si>
+  <si>
+    <t>lab103_lunes_elenamolina_fisica_i_12y30_15y30</t>
+  </si>
+  <si>
+    <t>Juves</t>
+  </si>
+  <si>
+    <t>lab103_juves_isabelruiz_matematicas_i_12y30_15y30</t>
+  </si>
+  <si>
+    <t>Cálculo Diferencial</t>
+  </si>
+  <si>
+    <t>marialopez</t>
+  </si>
+  <si>
+    <t>Domingo</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>06-12-2024</t>
+  </si>
+  <si>
+    <t>lab103_domingo_marialopez_calculo_diferencial_13y00_15y00</t>
+  </si>
+  <si>
     <t>LAB-104</t>
   </si>
   <si>
@@ -311,15 +395,15 @@
     <t>HS40</t>
   </si>
   <si>
+    <t>31-12-2024</t>
+  </si>
+  <si>
+    <t>lab104_martes_doloresjimenez_fisica_i_12y00_14y00</t>
+  </si>
+  <si>
     <t>LAB-105</t>
   </si>
   <si>
-    <t>Cálculo Diferencial</t>
-  </si>
-  <si>
-    <t>marialopez</t>
-  </si>
-  <si>
     <t>18:00:00</t>
   </si>
   <si>
@@ -338,9 +422,6 @@
     <t>Desarrollo Web</t>
   </si>
   <si>
-    <t>elenamolina</t>
-  </si>
-  <si>
     <t>HS17</t>
   </si>
   <si>
@@ -420,6 +501,24 @@
   </si>
   <si>
     <t>HS36</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>12-12-2024</t>
+  </si>
+  <si>
+    <t>lab106_juves_rosacastro_calculo_integral_16y00_20y00</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>lab106_miercoles_rosacastro_calculo_integral_23y00_24y00</t>
   </si>
 </sst>
 </file>
@@ -464,16 +563,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="25.0" customWidth="true"/>
-    <col min="2" max="2" width="45.0" customWidth="true"/>
-    <col min="3" max="3" width="30.0" customWidth="true"/>
-    <col min="4" max="4" width="20.0" customWidth="true"/>
-    <col min="5" max="5" width="15.0" customWidth="true"/>
+    <col min="2" max="2" width="30.0" customWidth="true"/>
+    <col min="3" max="3" width="45.0" customWidth="true"/>
+    <col min="4" max="4" width="30.0" customWidth="true"/>
+    <col min="5" max="5" width="20.0" customWidth="true"/>
     <col min="6" max="6" width="15.0" customWidth="true"/>
-    <col min="7" max="7" width="90.0" customWidth="true"/>
+    <col min="7" max="7" width="15.0" customWidth="true"/>
+    <col min="8" max="8" width="90.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,925 +598,1256 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>21</v>
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>19</v>
+      </c>
+      <c r="H5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>19</v>
+      </c>
+      <c r="H6" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>19</v>
+      </c>
+      <c r="H7" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>35</v>
+        <v>19</v>
+      </c>
+      <c r="H8" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>43</v>
+      </c>
+      <c r="H9" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" t="s">
         <v>42</v>
       </c>
-      <c r="D10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" t="s">
-        <v>39</v>
-      </c>
       <c r="G10" t="s">
-        <v>43</v>
+        <v>19</v>
+      </c>
+      <c r="H10" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G11" t="s">
-        <v>46</v>
+        <v>19</v>
+      </c>
+      <c r="H11" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G12" t="s">
-        <v>49</v>
+        <v>19</v>
+      </c>
+      <c r="H12" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F13" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G13" t="s">
-        <v>52</v>
+        <v>19</v>
+      </c>
+      <c r="H13" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F14" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G14" t="s">
-        <v>54</v>
+        <v>19</v>
+      </c>
+      <c r="H14" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F15" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G15" t="s">
-        <v>56</v>
+        <v>19</v>
+      </c>
+      <c r="H15" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="E16" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="F16" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G16" t="s">
-        <v>61</v>
+        <v>65</v>
+      </c>
+      <c r="H16" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="F17" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="G17" t="s">
-        <v>64</v>
+        <v>70</v>
+      </c>
+      <c r="H17" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D18" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F18" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="G18" t="s">
-        <v>67</v>
+        <v>19</v>
+      </c>
+      <c r="H18" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E19" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F19" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="G19" t="s">
-        <v>70</v>
+        <v>19</v>
+      </c>
+      <c r="H19" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E20" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F20" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="G20" t="s">
-        <v>73</v>
+        <v>19</v>
+      </c>
+      <c r="H20" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" t="s">
         <v>74</v>
       </c>
-      <c r="D21" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" t="s">
-        <v>39</v>
-      </c>
-      <c r="F21" t="s">
-        <v>60</v>
-      </c>
       <c r="G21" t="s">
-        <v>75</v>
+        <v>19</v>
+      </c>
+      <c r="H21" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E22" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F22" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="G22" t="s">
-        <v>77</v>
+        <v>19</v>
+      </c>
+      <c r="H22" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C23" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D23" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="F23" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G23" t="s">
-        <v>82</v>
+        <v>19</v>
+      </c>
+      <c r="H23" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="E24" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="F24" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G24" t="s">
-        <v>85</v>
+        <v>19</v>
+      </c>
+      <c r="H24" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="C25" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D25" t="s">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="E25" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="F25" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G25" t="s">
-        <v>88</v>
+        <v>96</v>
+      </c>
+      <c r="H25" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="D26" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="E26" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="F26" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G26" t="s">
-        <v>91</v>
+        <v>96</v>
+      </c>
+      <c r="H26" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C27" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D27" t="s">
-        <v>28</v>
+        <v>102</v>
       </c>
       <c r="E27" t="s">
-        <v>60</v>
+        <v>103</v>
       </c>
       <c r="F27" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="G27" t="s">
-        <v>94</v>
+        <v>104</v>
+      </c>
+      <c r="H27" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="B28" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="C28" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D28" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="E28" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="F28" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="G28" t="s">
-        <v>96</v>
+        <v>19</v>
+      </c>
+      <c r="H28" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="C29" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="D29" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E29" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="F29" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="G29" t="s">
-        <v>98</v>
+        <v>19</v>
+      </c>
+      <c r="H29" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="C30" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="D30" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E30" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F30" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G30" t="s">
-        <v>103</v>
+        <v>19</v>
+      </c>
+      <c r="H30" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B31" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C31" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="D31" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E31" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F31" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G31" t="s">
-        <v>106</v>
+        <v>19</v>
+      </c>
+      <c r="H31" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B32" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="C32" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="D32" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E32" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F32" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G32" t="s">
-        <v>109</v>
+        <v>19</v>
+      </c>
+      <c r="H32" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B33" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C33" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="D33" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E33" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F33" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G33" t="s">
-        <v>112</v>
+        <v>19</v>
+      </c>
+      <c r="H33" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B34" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C34" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D34" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E34" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F34" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G34" t="s">
-        <v>115</v>
+        <v>19</v>
+      </c>
+      <c r="H34" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B35" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="C35" t="s">
-        <v>116</v>
+        <v>36</v>
       </c>
       <c r="D35" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="E35" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="F35" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="G35" t="s">
-        <v>117</v>
+        <v>127</v>
+      </c>
+      <c r="H35" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B36" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="C36" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="D36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E36" t="s">
-        <v>11</v>
+        <v>109</v>
       </c>
       <c r="F36" t="s">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="G36" t="s">
-        <v>121</v>
+        <v>19</v>
+      </c>
+      <c r="H36" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B37" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="C37" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="D37" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E37" t="s">
-        <v>11</v>
+        <v>109</v>
       </c>
       <c r="F37" t="s">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="G37" t="s">
-        <v>124</v>
+        <v>19</v>
+      </c>
+      <c r="H37" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B38" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="C38" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="D38" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E38" t="s">
-        <v>11</v>
+        <v>109</v>
       </c>
       <c r="F38" t="s">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="G38" t="s">
-        <v>127</v>
+        <v>19</v>
+      </c>
+      <c r="H38" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B39" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="C39" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="D39" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E39" t="s">
-        <v>11</v>
+        <v>109</v>
       </c>
       <c r="F39" t="s">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="G39" t="s">
-        <v>130</v>
+        <v>19</v>
+      </c>
+      <c r="H39" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B40" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C40" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="D40" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E40" t="s">
-        <v>11</v>
+        <v>109</v>
       </c>
       <c r="F40" t="s">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="G40" t="s">
-        <v>133</v>
+        <v>19</v>
+      </c>
+      <c r="H40" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B41" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="C41" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="D41" t="s">
+        <v>34</v>
+      </c>
+      <c r="E41" t="s">
+        <v>109</v>
+      </c>
+      <c r="F41" t="s">
+        <v>130</v>
+      </c>
+      <c r="G41" t="s">
+        <v>19</v>
+      </c>
+      <c r="H41" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>145</v>
+      </c>
+      <c r="B42" t="s">
+        <v>146</v>
+      </c>
+      <c r="C42" t="s">
+        <v>147</v>
+      </c>
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42" t="s">
+        <v>19</v>
+      </c>
+      <c r="H42" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>145</v>
+      </c>
+      <c r="B43" t="s">
+        <v>149</v>
+      </c>
+      <c r="C43" t="s">
+        <v>150</v>
+      </c>
+      <c r="D43" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" t="s">
+        <v>19</v>
+      </c>
+      <c r="H43" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>145</v>
+      </c>
+      <c r="B44" t="s">
+        <v>152</v>
+      </c>
+      <c r="C44" t="s">
+        <v>153</v>
+      </c>
+      <c r="D44" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44" t="s">
+        <v>19</v>
+      </c>
+      <c r="H44" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>145</v>
+      </c>
+      <c r="B45" t="s">
+        <v>155</v>
+      </c>
+      <c r="C45" t="s">
+        <v>156</v>
+      </c>
+      <c r="D45" t="s">
+        <v>27</v>
+      </c>
+      <c r="E45" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>145</v>
+      </c>
+      <c r="B46" t="s">
+        <v>158</v>
+      </c>
+      <c r="C46" t="s">
+        <v>159</v>
+      </c>
+      <c r="D46" t="s">
         <v>31</v>
       </c>
-      <c r="E41" t="s">
-        <v>11</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="E46" t="s">
         <v>12</v>
       </c>
-      <c r="G41" t="s">
-        <v>135</v>
+      <c r="F46" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46" t="s">
+        <v>19</v>
+      </c>
+      <c r="H46" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>145</v>
+      </c>
+      <c r="B47" t="s">
+        <v>146</v>
+      </c>
+      <c r="C47" t="s">
+        <v>161</v>
+      </c>
+      <c r="D47" t="s">
+        <v>34</v>
+      </c>
+      <c r="E47" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47" t="s">
+        <v>19</v>
+      </c>
+      <c r="H47" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>145</v>
+      </c>
+      <c r="B48" t="s">
+        <v>146</v>
+      </c>
+      <c r="C48" t="s">
+        <v>141</v>
+      </c>
+      <c r="D48" t="s">
+        <v>98</v>
+      </c>
+      <c r="E48" t="s">
+        <v>69</v>
+      </c>
+      <c r="F48" t="s">
+        <v>163</v>
+      </c>
+      <c r="G48" t="s">
+        <v>164</v>
+      </c>
+      <c r="H48" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>145</v>
+      </c>
+      <c r="B49" t="s">
+        <v>146</v>
+      </c>
+      <c r="C49" t="s">
+        <v>141</v>
+      </c>
+      <c r="D49" t="s">
+        <v>67</v>
+      </c>
+      <c r="E49" t="s">
+        <v>166</v>
+      </c>
+      <c r="F49" t="s">
+        <v>167</v>
+      </c>
+      <c r="G49" t="s">
+        <v>70</v>
+      </c>
+      <c r="H49" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>

--- a/ProyectoAsistencia/ReporteClasesDeLaboratorio.xlsx
+++ b/ProyectoAsistencia/ReporteClasesDeLaboratorio.xlsx
@@ -12,9 +12,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t>Laboratorio</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="162">
+  <si>
+    <t>Nro Laboratorio</t>
   </si>
   <si>
     <t>Asignatura</t>
@@ -32,7 +32,472 @@
     <t>Hora Fin</t>
   </si>
   <si>
+    <t>Fecha Inicio</t>
+  </si>
+  <si>
     <t>Codigo de Horario</t>
+  </si>
+  <si>
+    <t>LAB-101</t>
+  </si>
+  <si>
+    <t>Estructuras Discretas</t>
+  </si>
+  <si>
+    <t>sofiadiaz</t>
+  </si>
+  <si>
+    <t>MARTES</t>
+  </si>
+  <si>
+    <t>08:00:00</t>
+  </si>
+  <si>
+    <t>10:00:00</t>
+  </si>
+  <si>
+    <t>08-12-2024</t>
+  </si>
+  <si>
+    <t>HS07</t>
+  </si>
+  <si>
+    <t>Sistemas Operativos</t>
+  </si>
+  <si>
+    <t>isabelruiz</t>
+  </si>
+  <si>
+    <t>MIERCOLES</t>
+  </si>
+  <si>
+    <t>14-12-2024</t>
+  </si>
+  <si>
+    <t>HS13</t>
+  </si>
+  <si>
+    <t>Análisis y Diseño de Sistemas</t>
+  </si>
+  <si>
+    <t>martinmoreno</t>
+  </si>
+  <si>
+    <t>JUEVES</t>
+  </si>
+  <si>
+    <t>20-12-2024</t>
+  </si>
+  <si>
+    <t>HS19</t>
+  </si>
+  <si>
+    <t>Computación en la Nube</t>
+  </si>
+  <si>
+    <t>raquelgarcia</t>
+  </si>
+  <si>
+    <t>VIERNES</t>
+  </si>
+  <si>
+    <t>26-12-2024</t>
+  </si>
+  <si>
+    <t>HS25</t>
+  </si>
+  <si>
+    <t>doloresjimenez</t>
+  </si>
+  <si>
+    <t>DOMINGO</t>
+  </si>
+  <si>
+    <t>07-01-2025</t>
+  </si>
+  <si>
+    <t>HS37</t>
+  </si>
+  <si>
+    <t>LAB-102</t>
+  </si>
+  <si>
+    <t>Matemáticas II</t>
+  </si>
+  <si>
+    <t>anagonzalez</t>
+  </si>
+  <si>
+    <t>LUNES</t>
+  </si>
+  <si>
+    <t>12:00:00</t>
+  </si>
+  <si>
+    <t>03-12-2024</t>
+  </si>
+  <si>
+    <t>HS02</t>
+  </si>
+  <si>
+    <t>Algoritmos y Estructuras de Datos</t>
+  </si>
+  <si>
+    <t>davidvazquez</t>
+  </si>
+  <si>
+    <t>09-12-2024</t>
+  </si>
+  <si>
+    <t>HS08</t>
+  </si>
+  <si>
+    <t>Redes de Computadoras</t>
+  </si>
+  <si>
+    <t>raultorres</t>
+  </si>
+  <si>
+    <t>15-12-2024</t>
+  </si>
+  <si>
+    <t>HS14</t>
+  </si>
+  <si>
+    <t>Administración de Proyectos de Software</t>
+  </si>
+  <si>
+    <t>paulamunoz</t>
+  </si>
+  <si>
+    <t>21-12-2024</t>
+  </si>
+  <si>
+    <t>HS20</t>
+  </si>
+  <si>
+    <t>Minería de Datos</t>
+  </si>
+  <si>
+    <t>francisconavarro</t>
+  </si>
+  <si>
+    <t>27-12-2024</t>
+  </si>
+  <si>
+    <t>HS26</t>
+  </si>
+  <si>
+    <t>tomasgutierrez</t>
+  </si>
+  <si>
+    <t>SABADO</t>
+  </si>
+  <si>
+    <t>02-01-2025</t>
+  </si>
+  <si>
+    <t>HS32</t>
+  </si>
+  <si>
+    <t>evacastillo</t>
+  </si>
+  <si>
+    <t>08-01-2025</t>
+  </si>
+  <si>
+    <t>HS38</t>
+  </si>
+  <si>
+    <t>LAB-103</t>
+  </si>
+  <si>
+    <t>Física I</t>
+  </si>
+  <si>
+    <t>luismartinez</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>04-12-2024</t>
+  </si>
+  <si>
+    <t>HS03</t>
+  </si>
+  <si>
+    <t>Programación I</t>
+  </si>
+  <si>
+    <t>laurafernandez</t>
+  </si>
+  <si>
+    <t>10-12-2024</t>
+  </si>
+  <si>
+    <t>HS09</t>
+  </si>
+  <si>
+    <t>Arquitectura de Computadores</t>
+  </si>
+  <si>
+    <t>carmenalvarez</t>
+  </si>
+  <si>
+    <t>16-12-2024</t>
+  </si>
+  <si>
+    <t>HS15</t>
+  </si>
+  <si>
+    <t>Inteligencia Artificial</t>
+  </si>
+  <si>
+    <t>antoniomendez</t>
+  </si>
+  <si>
+    <t>22-12-2024</t>
+  </si>
+  <si>
+    <t>HS21</t>
+  </si>
+  <si>
+    <t>Comunicaciones Digitales</t>
+  </si>
+  <si>
+    <t>angelromero</t>
+  </si>
+  <si>
+    <t>28-12-2024</t>
+  </si>
+  <si>
+    <t>HS27</t>
+  </si>
+  <si>
+    <t>veronicaluna</t>
+  </si>
+  <si>
+    <t>03-01-2025</t>
+  </si>
+  <si>
+    <t>HS33</t>
+  </si>
+  <si>
+    <t>cesarrojas</t>
+  </si>
+  <si>
+    <t>09-01-2025</t>
+  </si>
+  <si>
+    <t>HS39</t>
+  </si>
+  <si>
+    <t>LAB-104</t>
+  </si>
+  <si>
+    <t>Física II</t>
+  </si>
+  <si>
+    <t>carloshernandez</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>05-12-2024</t>
+  </si>
+  <si>
+    <t>HS04</t>
+  </si>
+  <si>
+    <t>Programación II</t>
+  </si>
+  <si>
+    <t>miguelsanchez</t>
+  </si>
+  <si>
+    <t>11-12-2024</t>
+  </si>
+  <si>
+    <t>HS10</t>
+  </si>
+  <si>
+    <t>Ingeniería de Software</t>
+  </si>
+  <si>
+    <t>javiergil</t>
+  </si>
+  <si>
+    <t>17-12-2024</t>
+  </si>
+  <si>
+    <t>HS16</t>
+  </si>
+  <si>
+    <t>Teoría de la Computación</t>
+  </si>
+  <si>
+    <t>claraserrano</t>
+  </si>
+  <si>
+    <t>23-12-2024</t>
+  </si>
+  <si>
+    <t>HS22</t>
+  </si>
+  <si>
+    <t>Sistemas Embebidos</t>
+  </si>
+  <si>
+    <t>teresaparedes</t>
+  </si>
+  <si>
+    <t>29-12-2024</t>
+  </si>
+  <si>
+    <t>HS28</t>
+  </si>
+  <si>
+    <t>oscarvega</t>
+  </si>
+  <si>
+    <t>04-01-2025</t>
+  </si>
+  <si>
+    <t>HS34</t>
+  </si>
+  <si>
+    <t>gabrielagonzalez</t>
+  </si>
+  <si>
+    <t>10-01-2025</t>
+  </si>
+  <si>
+    <t>HS40</t>
+  </si>
+  <si>
+    <t>LAB-105</t>
+  </si>
+  <si>
+    <t>Cálculo Diferencial</t>
+  </si>
+  <si>
+    <t>marialopez</t>
+  </si>
+  <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
+    <t>06-12-2024</t>
+  </si>
+  <si>
+    <t>HS05</t>
+  </si>
+  <si>
+    <t>Bases de Datos I</t>
+  </si>
+  <si>
+    <t>saramirez</t>
+  </si>
+  <si>
+    <t>12-12-2024</t>
+  </si>
+  <si>
+    <t>HS11</t>
+  </si>
+  <si>
+    <t>Desarrollo Web</t>
+  </si>
+  <si>
+    <t>elenamolina</t>
+  </si>
+  <si>
+    <t>18-12-2024</t>
+  </si>
+  <si>
+    <t>HS17</t>
+  </si>
+  <si>
+    <t>Ingeniería de Requerimientos</t>
+  </si>
+  <si>
+    <t>fernandoortiz</t>
+  </si>
+  <si>
+    <t>24-12-2024</t>
+  </si>
+  <si>
+    <t>HS23</t>
+  </si>
+  <si>
+    <t>luisanaponce</t>
+  </si>
+  <si>
+    <t>05-01-2025</t>
+  </si>
+  <si>
+    <t>HS35</t>
+  </si>
+  <si>
+    <t>LAB-106</t>
+  </si>
+  <si>
+    <t>Cálculo Integral</t>
+  </si>
+  <si>
+    <t>pedrogomez</t>
+  </si>
+  <si>
+    <t>07-12-2024</t>
+  </si>
+  <si>
+    <t>HS06</t>
+  </si>
+  <si>
+    <t>Bases de Datos II</t>
+  </si>
+  <si>
+    <t>josejimenez</t>
+  </si>
+  <si>
+    <t>13-12-2024</t>
+  </si>
+  <si>
+    <t>HS12</t>
+  </si>
+  <si>
+    <t>Desarrollo Móvil</t>
+  </si>
+  <si>
+    <t>manuelsuarez</t>
+  </si>
+  <si>
+    <t>19-12-2024</t>
+  </si>
+  <si>
+    <t>HS18</t>
+  </si>
+  <si>
+    <t>Seguridad Informática</t>
+  </si>
+  <si>
+    <t>beatrizcrespo</t>
+  </si>
+  <si>
+    <t>25-12-2024</t>
+  </si>
+  <si>
+    <t>HS24</t>
+  </si>
+  <si>
+    <t>estebanherrera</t>
+  </si>
+  <si>
+    <t>06-01-2025</t>
+  </si>
+  <si>
+    <t>HS36</t>
   </si>
 </sst>
 </file>
@@ -77,16 +542,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="30.0" customWidth="true"/>
+    <col min="1" max="1" width="25.0" customWidth="true"/>
     <col min="2" max="2" width="30.0" customWidth="true"/>
-    <col min="3" max="3" width="30.0" customWidth="true"/>
+    <col min="3" max="3" width="45.0" customWidth="true"/>
     <col min="4" max="4" width="30.0" customWidth="true"/>
-    <col min="5" max="5" width="30.0" customWidth="true"/>
-    <col min="6" max="6" width="30.0" customWidth="true"/>
-    <col min="7" max="7" width="30.0" customWidth="true"/>
+    <col min="5" max="5" width="20.0" customWidth="true"/>
+    <col min="6" max="6" width="15.0" customWidth="true"/>
+    <col min="7" max="7" width="15.0" customWidth="true"/>
+    <col min="8" max="8" width="90.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -111,6 +577,945 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" t="s">
+        <v>56</v>
+      </c>
+      <c r="H11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" t="s">
+        <v>60</v>
+      </c>
+      <c r="H12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" t="s">
+        <v>69</v>
+      </c>
+      <c r="H14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" t="s">
+        <v>73</v>
+      </c>
+      <c r="H15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H16" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17" t="s">
+        <v>81</v>
+      </c>
+      <c r="H17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" t="s">
+        <v>85</v>
+      </c>
+      <c r="H18" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19" t="s">
+        <v>88</v>
+      </c>
+      <c r="H19" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20" t="s">
+        <v>91</v>
+      </c>
+      <c r="H20" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>93</v>
+      </c>
+      <c r="B21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" t="s">
+        <v>68</v>
+      </c>
+      <c r="F21" t="s">
+        <v>96</v>
+      </c>
+      <c r="G21" t="s">
+        <v>97</v>
+      </c>
+      <c r="H21" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22" t="s">
+        <v>100</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>68</v>
+      </c>
+      <c r="F22" t="s">
+        <v>96</v>
+      </c>
+      <c r="G22" t="s">
+        <v>101</v>
+      </c>
+      <c r="H22" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" t="s">
+        <v>103</v>
+      </c>
+      <c r="C23" t="s">
+        <v>104</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" t="s">
+        <v>68</v>
+      </c>
+      <c r="F23" t="s">
+        <v>96</v>
+      </c>
+      <c r="G23" t="s">
+        <v>105</v>
+      </c>
+      <c r="H23" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>93</v>
+      </c>
+      <c r="B24" t="s">
+        <v>107</v>
+      </c>
+      <c r="C24" t="s">
+        <v>108</v>
+      </c>
+      <c r="D24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" t="s">
+        <v>96</v>
+      </c>
+      <c r="G24" t="s">
+        <v>109</v>
+      </c>
+      <c r="H24" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" t="s">
+        <v>111</v>
+      </c>
+      <c r="C25" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" t="s">
+        <v>68</v>
+      </c>
+      <c r="F25" t="s">
+        <v>96</v>
+      </c>
+      <c r="G25" t="s">
+        <v>113</v>
+      </c>
+      <c r="H25" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C26" t="s">
+        <v>115</v>
+      </c>
+      <c r="D26" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" t="s">
+        <v>68</v>
+      </c>
+      <c r="F26" t="s">
+        <v>96</v>
+      </c>
+      <c r="G26" t="s">
+        <v>116</v>
+      </c>
+      <c r="H26" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27" t="s">
+        <v>99</v>
+      </c>
+      <c r="C27" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" t="s">
+        <v>68</v>
+      </c>
+      <c r="F27" t="s">
+        <v>96</v>
+      </c>
+      <c r="G27" t="s">
+        <v>119</v>
+      </c>
+      <c r="H27" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>121</v>
+      </c>
+      <c r="B28" t="s">
+        <v>122</v>
+      </c>
+      <c r="C28" t="s">
+        <v>123</v>
+      </c>
+      <c r="D28" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" t="s">
+        <v>96</v>
+      </c>
+      <c r="F28" t="s">
+        <v>124</v>
+      </c>
+      <c r="G28" t="s">
+        <v>125</v>
+      </c>
+      <c r="H28" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>121</v>
+      </c>
+      <c r="B29" t="s">
+        <v>127</v>
+      </c>
+      <c r="C29" t="s">
+        <v>128</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>96</v>
+      </c>
+      <c r="F29" t="s">
+        <v>124</v>
+      </c>
+      <c r="G29" t="s">
+        <v>129</v>
+      </c>
+      <c r="H29" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>121</v>
+      </c>
+      <c r="B30" t="s">
+        <v>131</v>
+      </c>
+      <c r="C30" t="s">
+        <v>132</v>
+      </c>
+      <c r="D30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" t="s">
+        <v>96</v>
+      </c>
+      <c r="F30" t="s">
+        <v>124</v>
+      </c>
+      <c r="G30" t="s">
+        <v>133</v>
+      </c>
+      <c r="H30" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>121</v>
+      </c>
+      <c r="B31" t="s">
+        <v>135</v>
+      </c>
+      <c r="C31" t="s">
+        <v>136</v>
+      </c>
+      <c r="D31" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" t="s">
+        <v>96</v>
+      </c>
+      <c r="F31" t="s">
+        <v>124</v>
+      </c>
+      <c r="G31" t="s">
+        <v>137</v>
+      </c>
+      <c r="H31" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>121</v>
+      </c>
+      <c r="B32" t="s">
+        <v>122</v>
+      </c>
+      <c r="C32" t="s">
+        <v>139</v>
+      </c>
+      <c r="D32" t="s">
+        <v>59</v>
+      </c>
+      <c r="E32" t="s">
+        <v>96</v>
+      </c>
+      <c r="F32" t="s">
+        <v>124</v>
+      </c>
+      <c r="G32" t="s">
+        <v>140</v>
+      </c>
+      <c r="H32" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>142</v>
+      </c>
+      <c r="B33" t="s">
+        <v>143</v>
+      </c>
+      <c r="C33" t="s">
+        <v>144</v>
+      </c>
+      <c r="D33" t="s">
+        <v>38</v>
+      </c>
+      <c r="E33" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" t="s">
+        <v>145</v>
+      </c>
+      <c r="H33" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>142</v>
+      </c>
+      <c r="B34" t="s">
+        <v>147</v>
+      </c>
+      <c r="C34" t="s">
+        <v>148</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" t="s">
+        <v>149</v>
+      </c>
+      <c r="H34" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>142</v>
+      </c>
+      <c r="B35" t="s">
+        <v>151</v>
+      </c>
+      <c r="C35" t="s">
+        <v>152</v>
+      </c>
+      <c r="D35" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" t="s">
+        <v>153</v>
+      </c>
+      <c r="H35" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>142</v>
+      </c>
+      <c r="B36" t="s">
+        <v>155</v>
+      </c>
+      <c r="C36" t="s">
+        <v>156</v>
+      </c>
+      <c r="D36" t="s">
+        <v>23</v>
+      </c>
+      <c r="E36" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" t="s">
+        <v>157</v>
+      </c>
+      <c r="H36" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>142</v>
+      </c>
+      <c r="B37" t="s">
+        <v>143</v>
+      </c>
+      <c r="C37" t="s">
+        <v>159</v>
+      </c>
+      <c r="D37" t="s">
+        <v>59</v>
+      </c>
+      <c r="E37" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" t="s">
+        <v>160</v>
+      </c>
+      <c r="H37" t="s">
+        <v>161</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/ProyectoAsistencia/ReporteClasesDeLaboratorio.xlsx
+++ b/ProyectoAsistencia/ReporteClasesDeLaboratorio.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="177">
   <si>
     <t>Nro Laboratorio</t>
   </si>
@@ -41,6 +41,27 @@
     <t>LAB-101</t>
   </si>
   <si>
+    <t>Matemáticas I</t>
+  </si>
+  <si>
+    <t>juanperez</t>
+  </si>
+  <si>
+    <t>LUNES</t>
+  </si>
+  <si>
+    <t>08:00:00</t>
+  </si>
+  <si>
+    <t>10:00:00</t>
+  </si>
+  <si>
+    <t>02-12-2024</t>
+  </si>
+  <si>
+    <t>HS01</t>
+  </si>
+  <si>
     <t>Estructuras Discretas</t>
   </si>
   <si>
@@ -50,12 +71,6 @@
     <t>MARTES</t>
   </si>
   <si>
-    <t>08:00:00</t>
-  </si>
-  <si>
-    <t>10:00:00</t>
-  </si>
-  <si>
     <t>08-12-2024</t>
   </si>
   <si>
@@ -107,6 +122,18 @@
     <t>HS25</t>
   </si>
   <si>
+    <t>adrianasantos</t>
+  </si>
+  <si>
+    <t>SABADO</t>
+  </si>
+  <si>
+    <t>01-01-2025</t>
+  </si>
+  <si>
+    <t>HS31</t>
+  </si>
+  <si>
     <t>doloresjimenez</t>
   </si>
   <si>
@@ -128,9 +155,6 @@
     <t>anagonzalez</t>
   </si>
   <si>
-    <t>LUNES</t>
-  </si>
-  <si>
     <t>12:00:00</t>
   </si>
   <si>
@@ -191,9 +215,6 @@
     <t>tomasgutierrez</t>
   </si>
   <si>
-    <t>SABADO</t>
-  </si>
-  <si>
     <t>02-01-2025</t>
   </si>
   <si>
@@ -431,6 +452,18 @@
     <t>HS23</t>
   </si>
   <si>
+    <t>Ética Profesional</t>
+  </si>
+  <si>
+    <t>rosacastro</t>
+  </si>
+  <si>
+    <t>30-12-2024</t>
+  </si>
+  <si>
+    <t>HS29</t>
+  </si>
+  <si>
     <t>luisanaponce</t>
   </si>
   <si>
@@ -489,6 +522,18 @@
   </si>
   <si>
     <t>HS24</t>
+  </si>
+  <si>
+    <t>Economía y Gestión de la Tecnología</t>
+  </si>
+  <si>
+    <t>victorsalazar</t>
+  </si>
+  <si>
+    <t>31-12-2024</t>
+  </si>
+  <si>
+    <t>HS30</t>
   </si>
   <si>
     <t>estebanherrera</t>
@@ -542,7 +587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="25.0" customWidth="true"/>
@@ -690,13 +735,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
         <v>12</v>
@@ -705,82 +750,82 @@
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
         <v>36</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>37</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" t="s">
         <v>38</v>
       </c>
-      <c r="E7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
         <v>39</v>
-      </c>
-      <c r="G7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" t="s">
         <v>42</v>
       </c>
-      <c r="C8" t="s">
+      <c r="H8" t="s">
         <v>43</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" t="s">
-        <v>44</v>
-      </c>
-      <c r="H8" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" t="s">
         <v>46</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" t="s">
         <v>47</v>
-      </c>
-      <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" t="s">
-        <v>39</v>
       </c>
       <c r="G9" t="s">
         <v>48</v>
@@ -791,7 +836,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B10" t="s">
         <v>50</v>
@@ -800,13 +845,13 @@
         <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E10" t="s">
         <v>13</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G10" t="s">
         <v>52</v>
@@ -817,7 +862,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B11" t="s">
         <v>54</v>
@@ -826,13 +871,13 @@
         <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G11" t="s">
         <v>56</v>
@@ -843,22 +888,22 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="E12" t="s">
         <v>13</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G12" t="s">
         <v>60</v>
@@ -869,178 +914,178 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" t="s">
         <v>13</v>
       </c>
       <c r="F13" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" t="s">
         <v>66</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" t="s">
+        <v>47</v>
+      </c>
+      <c r="G14" t="s">
         <v>67</v>
       </c>
-      <c r="D14" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" t="s">
-        <v>39</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="H14" t="s">
         <v>68</v>
-      </c>
-      <c r="G14" t="s">
-        <v>69</v>
-      </c>
-      <c r="H14" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="B15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G15" t="s">
+        <v>70</v>
+      </c>
+      <c r="H15" t="s">
         <v>71</v>
-      </c>
-      <c r="C15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15" t="s">
-        <v>68</v>
-      </c>
-      <c r="G15" t="s">
-        <v>73</v>
-      </c>
-      <c r="H15" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" t="s">
         <v>75</v>
       </c>
-      <c r="C16" t="s">
+      <c r="G16" t="s">
         <v>76</v>
       </c>
-      <c r="D16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" t="s">
-        <v>68</v>
-      </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>77</v>
-      </c>
-      <c r="H16" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" t="s">
         <v>79</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" t="s">
+        <v>75</v>
+      </c>
+      <c r="G17" t="s">
         <v>80</v>
       </c>
-      <c r="D17" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" t="s">
-        <v>39</v>
-      </c>
-      <c r="F17" t="s">
-        <v>68</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>81</v>
-      </c>
-      <c r="H17" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" t="s">
         <v>83</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" t="s">
+        <v>75</v>
+      </c>
+      <c r="G18" t="s">
         <v>84</v>
       </c>
-      <c r="D18" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" t="s">
-        <v>39</v>
-      </c>
-      <c r="F18" t="s">
-        <v>68</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>85</v>
-      </c>
-      <c r="H18" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
         <v>87</v>
       </c>
       <c r="D19" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="E19" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F19" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G19" t="s">
         <v>88</v>
@@ -1051,178 +1096,178 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E20" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="B21" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" t="s">
         <v>94</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" t="s">
+        <v>75</v>
+      </c>
+      <c r="G21" t="s">
         <v>95</v>
       </c>
-      <c r="D21" t="s">
-        <v>38</v>
-      </c>
-      <c r="E21" t="s">
-        <v>68</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="H21" t="s">
         <v>96</v>
-      </c>
-      <c r="G21" t="s">
-        <v>97</v>
-      </c>
-      <c r="H21" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="B22" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22" t="s">
+        <v>75</v>
+      </c>
+      <c r="G22" t="s">
+        <v>98</v>
+      </c>
+      <c r="H22" t="s">
         <v>99</v>
-      </c>
-      <c r="C22" t="s">
-        <v>100</v>
-      </c>
-      <c r="D22" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" t="s">
-        <v>68</v>
-      </c>
-      <c r="F22" t="s">
-        <v>96</v>
-      </c>
-      <c r="G22" t="s">
-        <v>101</v>
-      </c>
-      <c r="H22" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" t="s">
+        <v>102</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>75</v>
+      </c>
+      <c r="F23" t="s">
         <v>103</v>
       </c>
-      <c r="C23" t="s">
+      <c r="G23" t="s">
         <v>104</v>
       </c>
-      <c r="D23" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" t="s">
-        <v>68</v>
-      </c>
-      <c r="F23" t="s">
-        <v>96</v>
-      </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>105</v>
-      </c>
-      <c r="H23" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B24" t="s">
+        <v>106</v>
+      </c>
+      <c r="C24" t="s">
         <v>107</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" t="s">
+        <v>75</v>
+      </c>
+      <c r="F24" t="s">
+        <v>103</v>
+      </c>
+      <c r="G24" t="s">
         <v>108</v>
       </c>
-      <c r="D24" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24" t="s">
-        <v>68</v>
-      </c>
-      <c r="F24" t="s">
-        <v>96</v>
-      </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>109</v>
-      </c>
-      <c r="H24" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B25" t="s">
+        <v>110</v>
+      </c>
+      <c r="C25" t="s">
         <v>111</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" t="s">
+        <v>75</v>
+      </c>
+      <c r="F25" t="s">
+        <v>103</v>
+      </c>
+      <c r="G25" t="s">
         <v>112</v>
       </c>
-      <c r="D25" t="s">
-        <v>28</v>
-      </c>
-      <c r="E25" t="s">
-        <v>68</v>
-      </c>
-      <c r="F25" t="s">
-        <v>96</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>113</v>
-      </c>
-      <c r="H25" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s">
         <v>115</v>
       </c>
       <c r="D26" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="E26" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F26" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="G26" t="s">
         <v>116</v>
@@ -1233,152 +1278,152 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B27" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E27" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F27" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="G27" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H27" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="B28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C28" t="s">
         <v>122</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" t="s">
+        <v>75</v>
+      </c>
+      <c r="F28" t="s">
+        <v>103</v>
+      </c>
+      <c r="G28" t="s">
         <v>123</v>
       </c>
-      <c r="D28" t="s">
-        <v>38</v>
-      </c>
-      <c r="E28" t="s">
-        <v>96</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="H28" t="s">
         <v>124</v>
-      </c>
-      <c r="G28" t="s">
-        <v>125</v>
-      </c>
-      <c r="H28" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="B29" t="s">
+        <v>106</v>
+      </c>
+      <c r="C29" t="s">
+        <v>125</v>
+      </c>
+      <c r="D29" t="s">
+        <v>41</v>
+      </c>
+      <c r="E29" t="s">
+        <v>75</v>
+      </c>
+      <c r="F29" t="s">
+        <v>103</v>
+      </c>
+      <c r="G29" t="s">
+        <v>126</v>
+      </c>
+      <c r="H29" t="s">
         <v>127</v>
-      </c>
-      <c r="C29" t="s">
-        <v>128</v>
-      </c>
-      <c r="D29" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" t="s">
-        <v>96</v>
-      </c>
-      <c r="F29" t="s">
-        <v>124</v>
-      </c>
-      <c r="G29" t="s">
-        <v>129</v>
-      </c>
-      <c r="H29" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B30" t="s">
+        <v>129</v>
+      </c>
+      <c r="C30" t="s">
+        <v>130</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>103</v>
+      </c>
+      <c r="F30" t="s">
         <v>131</v>
       </c>
-      <c r="C30" t="s">
+      <c r="G30" t="s">
         <v>132</v>
       </c>
-      <c r="D30" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30" t="s">
-        <v>96</v>
-      </c>
-      <c r="F30" t="s">
-        <v>124</v>
-      </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>133</v>
-      </c>
-      <c r="H30" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B31" t="s">
+        <v>134</v>
+      </c>
+      <c r="C31" t="s">
         <v>135</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" t="s">
+        <v>103</v>
+      </c>
+      <c r="F31" t="s">
+        <v>131</v>
+      </c>
+      <c r="G31" t="s">
         <v>136</v>
       </c>
-      <c r="D31" t="s">
-        <v>23</v>
-      </c>
-      <c r="E31" t="s">
-        <v>96</v>
-      </c>
-      <c r="F31" t="s">
-        <v>124</v>
-      </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
         <v>137</v>
-      </c>
-      <c r="H31" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B32" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="C32" t="s">
         <v>139</v>
       </c>
       <c r="D32" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="E32" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F32" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="G32" t="s">
         <v>140</v>
@@ -1389,94 +1434,94 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
+        <v>128</v>
+      </c>
+      <c r="B33" t="s">
         <v>142</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>143</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" t="s">
+        <v>103</v>
+      </c>
+      <c r="F33" t="s">
+        <v>131</v>
+      </c>
+      <c r="G33" t="s">
         <v>144</v>
       </c>
-      <c r="D33" t="s">
-        <v>38</v>
-      </c>
-      <c r="E33" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
         <v>145</v>
-      </c>
-      <c r="H33" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="B34" t="s">
+        <v>146</v>
+      </c>
+      <c r="C34" t="s">
         <v>147</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
+        <v>33</v>
+      </c>
+      <c r="E34" t="s">
+        <v>103</v>
+      </c>
+      <c r="F34" t="s">
+        <v>131</v>
+      </c>
+      <c r="G34" t="s">
         <v>148</v>
       </c>
-      <c r="D34" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>149</v>
-      </c>
-      <c r="H34" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="B35" t="s">
+        <v>129</v>
+      </c>
+      <c r="C35" t="s">
+        <v>150</v>
+      </c>
+      <c r="D35" t="s">
+        <v>37</v>
+      </c>
+      <c r="E35" t="s">
+        <v>103</v>
+      </c>
+      <c r="F35" t="s">
+        <v>131</v>
+      </c>
+      <c r="G35" t="s">
         <v>151</v>
       </c>
-      <c r="C35" t="s">
+      <c r="H35" t="s">
         <v>152</v>
-      </c>
-      <c r="D35" t="s">
-        <v>18</v>
-      </c>
-      <c r="E35" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" t="s">
-        <v>13</v>
-      </c>
-      <c r="G35" t="s">
-        <v>153</v>
-      </c>
-      <c r="H35" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="B36" t="s">
+        <v>154</v>
+      </c>
+      <c r="C36" t="s">
         <v>155</v>
       </c>
-      <c r="C36" t="s">
-        <v>156</v>
-      </c>
       <c r="D36" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E36" t="s">
         <v>12</v>
@@ -1485,24 +1530,24 @@
         <v>13</v>
       </c>
       <c r="G36" t="s">
+        <v>156</v>
+      </c>
+      <c r="H36" t="s">
         <v>157</v>
-      </c>
-      <c r="H36" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="B37" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="C37" t="s">
         <v>159</v>
       </c>
       <c r="D37" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="E37" t="s">
         <v>12</v>
@@ -1515,6 +1560,110 @@
       </c>
       <c r="H37" t="s">
         <v>161</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>153</v>
+      </c>
+      <c r="B38" t="s">
+        <v>162</v>
+      </c>
+      <c r="C38" t="s">
+        <v>163</v>
+      </c>
+      <c r="D38" t="s">
+        <v>23</v>
+      </c>
+      <c r="E38" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" t="s">
+        <v>164</v>
+      </c>
+      <c r="H38" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>153</v>
+      </c>
+      <c r="B39" t="s">
+        <v>166</v>
+      </c>
+      <c r="C39" t="s">
+        <v>167</v>
+      </c>
+      <c r="D39" t="s">
+        <v>28</v>
+      </c>
+      <c r="E39" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" t="s">
+        <v>168</v>
+      </c>
+      <c r="H39" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>153</v>
+      </c>
+      <c r="B40" t="s">
+        <v>170</v>
+      </c>
+      <c r="C40" t="s">
+        <v>171</v>
+      </c>
+      <c r="D40" t="s">
+        <v>33</v>
+      </c>
+      <c r="E40" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" t="s">
+        <v>172</v>
+      </c>
+      <c r="H40" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>153</v>
+      </c>
+      <c r="B41" t="s">
+        <v>154</v>
+      </c>
+      <c r="C41" t="s">
+        <v>174</v>
+      </c>
+      <c r="D41" t="s">
+        <v>37</v>
+      </c>
+      <c r="E41" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41" t="s">
+        <v>175</v>
+      </c>
+      <c r="H41" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>
